--- a/artfynd/A 8439-2025 artfynd.xlsx
+++ b/artfynd/A 8439-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104313089</v>
+        <v>104313084</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619648.1226465412</v>
+        <v>619749</v>
       </c>
       <c r="R2" t="n">
-        <v>6956002.594143568</v>
+        <v>6955770</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104313085</v>
+        <v>104313089</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619690.4931913409</v>
+        <v>619648</v>
       </c>
       <c r="R3" t="n">
-        <v>6955962.806192697</v>
+        <v>6956002</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104313088</v>
+        <v>104313080</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619648.1226465412</v>
+        <v>619835</v>
       </c>
       <c r="R4" t="n">
-        <v>6956002.594143568</v>
+        <v>6955823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104313084</v>
+        <v>104313085</v>
       </c>
       <c r="B5" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619749.0102716079</v>
+        <v>619691</v>
       </c>
       <c r="R5" t="n">
-        <v>6955769.770837112</v>
+        <v>6955963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104313087</v>
+        <v>104313070</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619648.1226465412</v>
+        <v>619604</v>
       </c>
       <c r="R6" t="n">
-        <v>6956002.594143568</v>
+        <v>6956211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104313070</v>
+        <v>104313088</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619603.3176125826</v>
+        <v>619648</v>
       </c>
       <c r="R7" t="n">
-        <v>6956210.807617294</v>
+        <v>6956002</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1254,103 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104313087</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenbittjärnarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>619648</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6956002</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8439-2025 artfynd.xlsx
+++ b/artfynd/A 8439-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104313084</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104313089</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104313080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104313085</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104313070</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104313088</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104313087</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>